--- a/data/gravel not enough data/Tanglefoot Hardtack V2 2024.xlsx
+++ b/data/gravel not enough data/Tanglefoot Hardtack V2 2024.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/hardtail/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel not enough data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCD62D11-15A2-454C-A697-D0D40DC52B10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B042D92-1E24-4148-8170-7E3EA1AB63B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11160" yWindow="840" windowWidth="22540" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -272,9 +272,6 @@
     <t>no</t>
   </si>
   <si>
-    <t>us</t>
-  </si>
-  <si>
     <t>steel</t>
   </si>
   <si>
@@ -284,12 +281,6 @@
     <t>Tanglefoot</t>
   </si>
   <si>
-    <t>Hardtack</t>
-  </si>
-  <si>
-    <t>https://analogcycles.com/products/tanglefoot-cycles-hardtack-v2</t>
-  </si>
-  <si>
     <t>both</t>
   </si>
   <si>
@@ -339,13 +330,22 @@
   </si>
   <si>
     <t>internal</t>
+  </si>
+  <si>
+    <t>https://tanglefootcycles.com/tanglefoot/hardtack/</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>Hardtack V2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
@@ -389,11 +389,6 @@
       <name val="Roboto"/>
     </font>
     <font>
-      <b/>
-      <sz val="14"/>
-      <name val="Futura Medium"/>
-    </font>
-    <font>
       <sz val="14"/>
       <name val="Futura Medium"/>
     </font>
@@ -418,7 +413,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -428,7 +423,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -736,7 +730,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -744,7 +738,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -768,7 +762,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="22">
@@ -776,7 +770,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C7" s="3"/>
     </row>
@@ -785,22 +779,22 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>98</v>
       </c>
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
@@ -815,16 +809,16 @@
       <c r="C9" s="8">
         <v>560</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="8">
         <v>585</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="8">
         <v>610</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="8">
         <v>640</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="8">
         <v>690</v>
       </c>
       <c r="H9" s="7"/>
@@ -837,19 +831,19 @@
       <c r="B10" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="8">
         <v>375</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="8">
         <v>395</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="8">
         <v>415</v>
       </c>
-      <c r="F10" s="9">
+      <c r="F10" s="8">
         <v>430</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G10" s="8">
         <v>440</v>
       </c>
       <c r="H10" s="7"/>
@@ -862,21 +856,21 @@
         <v>7</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C11" s="8">
         <v>569</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="8">
         <v>598</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="8">
         <v>627</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F11" s="8">
         <v>652</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G11" s="8">
         <v>679</v>
       </c>
       <c r="H11" s="7"/>
@@ -887,21 +881,21 @@
         <v>8</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="C12" s="9">
+        <v>84</v>
+      </c>
+      <c r="C12" s="8">
         <v>425</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="8">
         <v>455</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="8">
         <v>485</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F12" s="8">
         <v>515</v>
       </c>
-      <c r="G12" s="9">
+      <c r="G12" s="8">
         <v>545</v>
       </c>
       <c r="H12" s="7"/>
@@ -912,21 +906,21 @@
         <v>13</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="C13" s="9">
+        <v>85</v>
+      </c>
+      <c r="C13" s="8">
         <v>69</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="8">
         <v>69</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="8">
         <v>69</v>
       </c>
-      <c r="F13" s="9">
+      <c r="F13" s="8">
         <v>69</v>
       </c>
-      <c r="G13" s="9">
+      <c r="G13" s="8">
         <v>69</v>
       </c>
       <c r="H13" s="7"/>
@@ -939,19 +933,19 @@
       <c r="B14" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C14" s="9">
+      <c r="C14" s="8">
         <v>50</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="8">
         <v>63</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="8">
         <v>63</v>
       </c>
-      <c r="F14" s="9">
+      <c r="F14" s="8">
         <v>63</v>
       </c>
-      <c r="G14" s="9">
+      <c r="G14" s="8">
         <v>63</v>
       </c>
       <c r="H14" s="7"/>
@@ -962,21 +956,21 @@
         <v>11</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="C15" s="9">
+        <v>86</v>
+      </c>
+      <c r="C15" s="8">
         <v>50</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="8">
         <v>50</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="8">
         <v>50</v>
       </c>
-      <c r="F15" s="9">
+      <c r="F15" s="8">
         <v>50</v>
       </c>
-      <c r="G15" s="9">
+      <c r="G15" s="8">
         <v>50</v>
       </c>
       <c r="H15" s="7"/>
@@ -984,24 +978,24 @@
     </row>
     <row r="16" spans="1:11" ht="21">
       <c r="A16" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="C16" s="9">
+        <v>87</v>
+      </c>
+      <c r="C16" s="8">
         <v>306</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D16" s="8">
         <v>306</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="8">
         <v>306</v>
       </c>
-      <c r="F16" s="9">
+      <c r="F16" s="8">
         <v>306</v>
       </c>
-      <c r="G16" s="9">
+      <c r="G16" s="8">
         <v>306</v>
       </c>
       <c r="H16" s="7"/>
@@ -1012,21 +1006,21 @@
         <v>12</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="C17" s="9">
+        <v>88</v>
+      </c>
+      <c r="C17" s="8">
         <v>71</v>
       </c>
-      <c r="D17" s="9">
+      <c r="D17" s="8">
         <v>71</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="8">
         <v>71</v>
       </c>
-      <c r="F17" s="9">
+      <c r="F17" s="8">
         <v>71</v>
       </c>
-      <c r="G17" s="9">
+      <c r="G17" s="8">
         <v>71</v>
       </c>
       <c r="H17" s="7"/>
@@ -1037,21 +1031,21 @@
         <v>10</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="C18" s="9">
+        <v>89</v>
+      </c>
+      <c r="C18" s="8">
         <v>450</v>
       </c>
-      <c r="D18" s="9">
+      <c r="D18" s="8">
         <v>450</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="8">
         <v>450</v>
       </c>
-      <c r="F18" s="9">
+      <c r="F18" s="8">
         <v>450</v>
       </c>
-      <c r="G18" s="9">
+      <c r="G18" s="8">
         <v>450</v>
       </c>
       <c r="H18" s="7"/>
@@ -1061,21 +1055,21 @@
         <v>24</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="C19" s="9">
+        <v>90</v>
+      </c>
+      <c r="C19" s="8">
         <v>757</v>
       </c>
-      <c r="D19" s="9">
+      <c r="D19" s="8">
         <v>784</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="8">
         <v>810</v>
       </c>
-      <c r="F19" s="9">
+      <c r="F19" s="8">
         <v>840</v>
       </c>
-      <c r="G19" s="9">
+      <c r="G19" s="8">
         <v>879</v>
       </c>
     </row>
@@ -1221,41 +1215,41 @@
         <v>152.4</v>
       </c>
       <c r="D32">
-        <f>AVERAGE(D34,C35)*2.54</f>
+        <f>D34*2.54</f>
         <v>162.56</v>
       </c>
       <c r="E32">
-        <f t="shared" ref="E32:G32" si="2">AVERAGE(E34,D35)*2.54</f>
+        <f>E34*2.54</f>
         <v>172.72</v>
       </c>
       <c r="F32">
-        <f t="shared" si="2"/>
+        <f>F34*2.54</f>
         <v>180.34</v>
       </c>
       <c r="G32">
-        <f t="shared" si="2"/>
-        <v>186.69</v>
+        <f>G34*2.54</f>
+        <v>187.96</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
         <v>29</v>
       </c>
-      <c r="C33" s="1">
-        <f>D32</f>
+      <c r="C33">
+        <f>C35*2.54</f>
         <v>162.56</v>
       </c>
-      <c r="D33" s="1">
-        <f t="shared" ref="D33:F33" si="3">E32</f>
+      <c r="D33">
+        <f>D35*2.54</f>
         <v>172.72</v>
       </c>
-      <c r="E33" s="1">
-        <f t="shared" si="3"/>
+      <c r="E33">
+        <f>E35*2.54</f>
         <v>180.34</v>
       </c>
-      <c r="F33" s="1">
-        <f t="shared" si="3"/>
-        <v>186.69</v>
+      <c r="F33">
+        <f>F35*2.54</f>
+        <v>185.42000000000002</v>
       </c>
       <c r="G33">
         <f>G35*2.54</f>
@@ -1320,7 +1314,7 @@
         <v>70</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C37" s="6"/>
       <c r="D37" s="6"/>
@@ -1341,7 +1335,7 @@
         <v>32</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1481,7 +1475,7 @@
         <v>54</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1507,6 +1501,9 @@
       <c r="A64" t="s">
         <v>58</v>
       </c>
+      <c r="B64">
+        <v>1</v>
+      </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
@@ -1553,7 +1550,7 @@
         <v>64</v>
       </c>
       <c r="B70">
-        <v>1080</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -1572,7 +1569,7 @@
         <v>67</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel not enough data/Tanglefoot Hardtack V2 2024.xlsx
+++ b/data/gravel not enough data/Tanglefoot Hardtack V2 2024.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel not enough data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B042D92-1E24-4148-8170-7E3EA1AB63B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC0A555E-70B9-E34F-81BA-0E776AF15238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11160" yWindow="840" windowWidth="22540" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6260" yWindow="600" windowWidth="22540" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="103">
   <si>
     <t>brand</t>
   </si>
@@ -339,6 +339,9 @@
   </si>
   <si>
     <t>Hardtack V2</t>
+  </si>
+  <si>
+    <t>location</t>
   </si>
 </sst>
 </file>
@@ -719,7 +722,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K73"/>
+  <dimension ref="A1:K74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1211,23 +1214,23 @@
         <v>28</v>
       </c>
       <c r="C32">
-        <f>C34*2.54</f>
+        <f t="shared" ref="C32:G33" si="2">C34*2.54</f>
         <v>152.4</v>
       </c>
       <c r="D32">
-        <f>D34*2.54</f>
+        <f t="shared" si="2"/>
         <v>162.56</v>
       </c>
       <c r="E32">
-        <f>E34*2.54</f>
+        <f t="shared" si="2"/>
         <v>172.72</v>
       </c>
       <c r="F32">
-        <f>F34*2.54</f>
+        <f t="shared" si="2"/>
         <v>180.34</v>
       </c>
       <c r="G32">
-        <f>G34*2.54</f>
+        <f t="shared" si="2"/>
         <v>187.96</v>
       </c>
     </row>
@@ -1236,23 +1239,23 @@
         <v>29</v>
       </c>
       <c r="C33">
-        <f>C35*2.54</f>
+        <f t="shared" si="2"/>
         <v>162.56</v>
       </c>
       <c r="D33">
-        <f>D35*2.54</f>
+        <f t="shared" si="2"/>
         <v>172.72</v>
       </c>
       <c r="E33">
-        <f>E35*2.54</f>
+        <f t="shared" si="2"/>
         <v>180.34</v>
       </c>
       <c r="F33">
-        <f>F35*2.54</f>
+        <f t="shared" si="2"/>
         <v>185.42000000000002</v>
       </c>
       <c r="G33">
-        <f>G35*2.54</f>
+        <f t="shared" si="2"/>
         <v>203.2</v>
       </c>
     </row>
@@ -1572,6 +1575,11 @@
         <v>100</v>
       </c>
     </row>
+    <row r="74" spans="1:2">
+      <c r="A74" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel not enough data/Tanglefoot Hardtack V2 2024.xlsx
+++ b/data/gravel not enough data/Tanglefoot Hardtack V2 2024.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel not enough data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC0A555E-70B9-E34F-81BA-0E776AF15238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01DCB57E-490F-C046-AF4C-F4A008D77682}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6260" yWindow="600" windowWidth="22540" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33920" yWindow="-21140" windowWidth="22540" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -348,7 +348,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
@@ -395,6 +395,11 @@
       <sz val="14"/>
       <name val="Futura Medium"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF444444"/>
+      <name val="Futura Medium"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -416,7 +421,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -426,6 +431,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -831,7 +837,7 @@
       <c r="A10" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="9" t="s">
         <v>72</v>
       </c>
       <c r="C10" s="8">
@@ -854,11 +860,11 @@
       <c r="J10" s="6"/>
       <c r="K10" s="6"/>
     </row>
-    <row r="11" spans="1:11" ht="21">
+    <row r="11" spans="1:11">
       <c r="A11" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="9" t="s">
         <v>83</v>
       </c>
       <c r="C11" s="8">
@@ -879,11 +885,11 @@
       <c r="H11" s="7"/>
       <c r="I11" s="7"/>
     </row>
-    <row r="12" spans="1:11" ht="21">
+    <row r="12" spans="1:11">
       <c r="A12" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="9" t="s">
         <v>84</v>
       </c>
       <c r="C12" s="8">
@@ -904,11 +910,11 @@
       <c r="H12" s="7"/>
       <c r="I12" s="7"/>
     </row>
-    <row r="13" spans="1:11" ht="21">
+    <row r="13" spans="1:11">
       <c r="A13" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="9" t="s">
         <v>85</v>
       </c>
       <c r="C13" s="8">
@@ -929,11 +935,11 @@
       <c r="H13" s="7"/>
       <c r="I13" s="7"/>
     </row>
-    <row r="14" spans="1:11" ht="21">
+    <row r="14" spans="1:11">
       <c r="A14" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="9" t="s">
         <v>74</v>
       </c>
       <c r="C14" s="8">
@@ -954,11 +960,11 @@
       <c r="H14" s="7"/>
       <c r="I14" s="7"/>
     </row>
-    <row r="15" spans="1:11" ht="21">
+    <row r="15" spans="1:11">
       <c r="A15" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="9" t="s">
         <v>86</v>
       </c>
       <c r="C15" s="8">
@@ -979,11 +985,11 @@
       <c r="H15" s="7"/>
       <c r="I15" s="7"/>
     </row>
-    <row r="16" spans="1:11" ht="21">
+    <row r="16" spans="1:11">
       <c r="A16" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="9" t="s">
         <v>87</v>
       </c>
       <c r="C16" s="8">
@@ -1004,11 +1010,11 @@
       <c r="H16" s="7"/>
       <c r="I16" s="7"/>
     </row>
-    <row r="17" spans="1:9" ht="21">
+    <row r="17" spans="1:9">
       <c r="A17" t="s">
         <v>12</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C17" s="8">
@@ -1029,11 +1035,11 @@
       <c r="H17" s="7"/>
       <c r="I17" s="7"/>
     </row>
-    <row r="18" spans="1:9" ht="21">
+    <row r="18" spans="1:9">
       <c r="A18" t="s">
         <v>10</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="9" t="s">
         <v>89</v>
       </c>
       <c r="C18" s="8">
@@ -1053,11 +1059,11 @@
       </c>
       <c r="H18" s="7"/>
     </row>
-    <row r="19" spans="1:9" ht="21">
+    <row r="19" spans="1:9">
       <c r="A19" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="9" t="s">
         <v>90</v>
       </c>
       <c r="C19" s="8">
@@ -1101,7 +1107,7 @@
         <v>17</v>
       </c>
       <c r="B22" s="5"/>
-      <c r="C22" s="6"/>
+      <c r="C22" s="4"/>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
